--- a/神社檔案/鄉後12_整理.xlsx
+++ b/神社檔案/鄉後12_整理.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaish_mac/Desktop/DRHS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaish_mac/Desktop/DRHS/for github/mapu2/神社檔案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB1458-39EF-5E46-8AFD-900D9D2276F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0DF5D2-FE4D-0940-AC3A-E1DD61578D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="神社資料" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="12" customHeight="1">
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" s="2">
         <v>201</v>
       </c>
